--- a/pipeline/1_index_construction/indices_manifest.xlsx
+++ b/pipeline/1_index_construction/indices_manifest.xlsx
@@ -540,11 +540,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -629,7 +629,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>E:\\OneDrive\\Studia\\Studia magisterskie\\Masterarbeit 2 - Sozialwissenschaften\\data\\Sat_data_curated</t>
+          <t>CONFIG:sat_data_curated</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E:\\OneDrive\\Studia\\Studia magisterskie\\Masterarbeit 2 - Sozialwissenschaften\\data\\vector\\freguesia.gpkg</t>
+          <t>CONFIG:repo_data_dir/parishes.geojson</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>freguesia_id</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>E:\\OneDrive\\Studia\\Studia magisterskie\\Masterarbeit 2 - Sozialwissenschaften\\data\\outputs\\indices</t>
+          <t>CONFIG:outputs_indices_dir</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>helpers</t>
+          <t>global_defaults</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>age_bins</t>
+          <t>fractional_allocation_threshold_m</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{"pre_1975": {"codes": [1], "mid_year": 1965, "exclude": false}, "1975_1985": {"codes": [2], "mid_year": 1980, "exclude": false}, "1985_1995": {"codes": [3], "mid_year": 1990, "exclude": false}, "1995_2005": {"codes": [4], "mid_year": 2000, "exclude": false}, "2005_2015": {"codes": [5], "mid_year": 2010, "exclude": false}, "2015_2020": {"codes": [6], "mid_year": null, "exclude": true}}</t>
+          <t>400</t>
         </is>
       </c>
     </row>
@@ -794,10 +794,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>age_bins</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{"pre_1975": {"codes": [1], "mid_year": 1965, "exclude": false}, "1975_1985": {"codes": [2], "mid_year": 1980, "exclude": false}, "1985_1995": {"codes": [3], "mid_year": 1990, "exclude": false}, "1995_2005": {"codes": [4], "mid_year": 2000, "exclude": false}, "2005_2015": {"codes": [5], "mid_year": 2010, "exclude": false}, "2015_2020": {"codes": [6], "mid_year": null, "exclude": true}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>helpers</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>functions_required_in_runner</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>["recode_age_midyear(age_class, age_bins)", "is_age_bin(age_class, bin_name, age_bins)"]</t>
         </is>
@@ -1190,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1199,7 +1216,7 @@
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="57" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="49" customWidth="1" min="10" max="10"/>
@@ -1465,7 +1482,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>res_volume &gt; 0 &amp;&amp; pop &gt; 0</t>
+          <t>(res_volume &gt; 0) &amp;&amp; (pop &gt; 0)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1520,7 +1537,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>res_volume &gt; 0 &amp;&amp; pop &gt; 0</t>
+          <t>(res_volume &gt; 0) &amp;&amp; (pop &gt; 0)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1571,7 +1588,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>res_volume &gt; 0 &amp;&amp; mid_year != null</t>
+          <t>(res_volume &gt; 0) &amp;&amp; (mid_year != null)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1944,7 +1961,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>res_area &gt; 0 &amp;&amp; pop &gt; 0</t>
+          <t>(res_area &gt; 0) &amp;&amp; (pop &gt; 0)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1995,7 +2012,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>pop &gt; 0 &amp;&amp; res_area &gt; 0</t>
+          <t>(pop &gt; 0) &amp;&amp; (res_area &gt; 0)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2050,7 +2067,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>pop &gt; 0 &amp;&amp; res_area &gt; 0</t>
+          <t>(pop &gt; 0) &amp;&amp; (res_area &gt; 0)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2101,7 +2118,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>res_volume &gt; 0 &amp;&amp; mid_year != null</t>
+          <t>(res_volume &gt; 0) &amp;&amp; (mid_year != null)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2152,7 +2169,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>res_volume &gt; 0 &amp;&amp; mid_year != null</t>
+          <t>(res_volume &gt; 0) &amp;&amp; (mid_year != null)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2203,7 +2220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>res_volume &gt; 0 &amp;&amp; mid_year != null</t>
+          <t>(res_volume &gt; 0) &amp;&amp; (mid_year != null)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2254,7 +2271,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>res_volume &gt; 0 &amp;&amp; (res_area + nres_area) &gt; 0</t>
+          <t>(res_volume &gt; 0) &amp;&amp; ((res_area + nres_area) &gt; 0)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2279,7 +2296,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita</t>
+          <t>ntl</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2289,52 +2306,44 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(ntl*res_share*pop)/res_volume as ratio of sums.</t>
+          <t>Total residential-attributed night-time light: sum(ntl_intensity * residential built-up share).</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>["NTL", "Surface", "Surface_NRES", "Population", "Volume"]</t>
+          <t>["NTL", "Surface", "Surface_NRES"]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>{"ntl": "NTL", "res_area": "Surface", "nres_area": "Surface_NRES", "pop": "Population", "res_volume": "Volume"}</t>
+          <t>{"ntl": "NTL", "res_area": "Surface", "nres_area": "Surface_NRES"}</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>ntl_res</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>res_volume &gt; 0 &amp;&amp; pop &gt; 0 &amp;&amp; (res_area + nres_area) &gt; 0</t>
+          <t>((res_area + nres_area) &gt; 0)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ratio_of_sums</t>
+          <t>sum</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ntl * (res_area / (res_area + nres_area)) * pop</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>res_volume</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ntl_per_res_vol_distrib</t>
+          <t>ntl_per_capita</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2344,48 +2353,52 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Distribution of ntl_per_res_vol across cells weighted by res_volume.</t>
+          <t>Residential-attributed night-time light per capita: sum(ntl_intensity * residential built-up share) / sum(population).</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>["NTL", "Surface", "Surface_NRES", "Volume"]</t>
+          <t>["NTL", "Surface", "Surface_NRES", "Population"]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>{"ntl": "NTL", "res_area": "Surface", "nres_area": "Surface_NRES", "res_volume": "Volume"}</t>
+          <t>{"ntl": "NTL", "res_area": "Surface", "nres_area": "Surface_NRES", "pop": "Population"}</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>ntl_res / pop</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>res_volume &gt; 0 &amp;&amp; (res_area + nres_area) &gt; 0</t>
+          <t>(pop &gt; 0) &amp;&amp; ((res_area + nres_area) &gt; 0)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>weighted_distribution</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>res_volume</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>ratio_of_sums</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ntl * (res_area / (res_area + nres_area))</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita_distrib</t>
+          <t>energy_per_vol_per_capita</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2395,7 +2408,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Distribution of (ntl*res_share*pop)/res_volume across cells, weighted by population.</t>
+          <t>(ntl*res_share*pop)/res_volume as ratio of sums.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2410,73 +2423,77 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>proxy</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>res_volume &gt; 0 &amp;&amp; pop &gt; 0 &amp;&amp; (res_area + nres_area) &gt; 0</t>
+          <t>(res_volume &gt; 0) &amp;&amp; (pop &gt; 0) &amp;&amp; ((res_area + nres_area) &gt; 0)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>weighted_distribution</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>ratio_of_sums</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ntl * (res_area / (res_area + nres_area)) * pop</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>res_volume</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>delta_pm_25</t>
+          <t>ntl_per_res_vol_distrib</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Heating by combustion</t>
+          <t>Energy consumption proxies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PM2.5 delta (heating season vs rest of year), population-weighted.</t>
+          <t>Distribution of ntl_per_res_vol across cells weighted by res_volume.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>["PM_2_5_delta", "Population"]</t>
+          <t>["NTL", "Surface", "Surface_NRES", "Volume"]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>{"delta": "PM_2_5_delta", "pop": "Population"}</t>
+          <t>{"ntl": "NTL", "res_area": "Surface", "nres_area": "Surface_NRES", "res_volume": "Volume"}</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>delta</t>
+          <t>val</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>pop &gt; 0</t>
+          <t>(res_volume &gt; 0) &amp;&amp; ((res_area + nres_area) &gt; 0)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>weighted_mean</t>
+          <t>weighted_distribution</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>res_volume</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -2487,42 +2504,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>standard_delta_pm_25</t>
+          <t>energy_per_vol_per_capita_distrib</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Heating by combustion</t>
+          <t>Energy consumption proxies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PM2.5 delta standardized by average PM2.5, population-weighted.</t>
+          <t>Distribution of (ntl*res_share*pop)/res_volume across cells, weighted by population.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>["PM_2_5_delta", "PM_2_5_average", "Population"]</t>
+          <t>["NTL", "Surface", "Surface_NRES", "Population", "Volume"]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>{"delta": "PM_2_5_delta", "avg": "PM_2_5_average", "pop": "Population"}</t>
+          <t>{"ntl": "NTL", "res_area": "Surface", "nres_area": "Surface_NRES", "pop": "Population", "res_volume": "Volume"}</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>std_delta</t>
+          <t>val</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>pop &gt; 0 &amp;&amp; avg &gt; 0</t>
+          <t>(res_volume &gt; 0) &amp;&amp; (pop &gt; 0) &amp;&amp; ((res_area + nres_area) &gt; 0)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>weighted_mean</t>
+          <t>weighted_distribution</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2538,7 +2555,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>delta_pm_25_per_capita</t>
+          <t>delta_pm_25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2548,7 +2565,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cell-level delta_pm25/population, averaged across populated cells.</t>
+          <t>PM2.5 delta (heating season vs rest of year), population-weighted.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2563,7 +2580,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>delta</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2573,10 +2590,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>weighted_mean</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -2585,7 +2606,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>delta_bc</t>
+          <t>standard_delta_pm_25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,27 +2616,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Black carbon delta, population-weighted.</t>
+          <t>PM2.5 delta standardized by average PM2.5, population-weighted.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>["BC_delta", "Population"]</t>
+          <t>["PM_2_5_delta", "PM_2_5_average", "Population"]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>{"delta": "BC_delta", "pop": "Population"}</t>
+          <t>{"delta": "PM_2_5_delta", "avg": "PM_2_5_average", "pop": "Population"}</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>delta</t>
+          <t>std_delta</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>pop &gt; 0</t>
+          <t>(pop &gt; 0) &amp;&amp; (avg &gt; 0)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2636,7 +2657,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>standard_delta_bc</t>
+          <t>delta_pm_25_per_capita</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2646,39 +2667,35 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BC delta standardized by average BC, population-weighted.</t>
+          <t>Cell-level delta_pm25/population, averaged across populated cells.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>["BC_delta", "BC_average", "Population"]</t>
+          <t>["PM_2_5_delta", "Population"]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>{"delta": "BC_delta", "avg": "BC_average", "pop": "Population"}</t>
+          <t>{"delta": "PM_2_5_delta", "pop": "Population"}</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>std_delta</t>
+          <t>val</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>pop &gt; 0 &amp;&amp; avg &gt; 0</t>
+          <t>pop &gt; 0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>weighted_mean</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2687,7 +2704,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>delta_bc_per_capita</t>
+          <t>delta_bc</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2697,7 +2714,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cell-level BC_delta/population, averaged across populated cells.</t>
+          <t>Black carbon delta, population-weighted.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2712,7 +2729,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>delta</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2722,10 +2739,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>weighted_mean</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2734,7 +2755,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>delta_oc</t>
+          <t>standard_delta_bc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2744,27 +2765,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Organic carbon delta, population-weighted.</t>
+          <t>BC delta standardized by average BC, population-weighted.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>["OC_delta", "Population"]</t>
+          <t>["BC_delta", "BC_average", "Population"]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>{"delta": "OC_delta", "pop": "Population"}</t>
+          <t>{"delta": "BC_delta", "avg": "BC_average", "pop": "Population"}</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>delta</t>
+          <t>std_delta</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>pop &gt; 0</t>
+          <t>(pop &gt; 0) &amp;&amp; (avg &gt; 0)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2785,7 +2806,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>standard_delta_oc</t>
+          <t>delta_bc_per_capita</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2795,39 +2816,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OC delta standardized by average OC, population-weighted.</t>
+          <t>Cell-level BC_delta/population, averaged across populated cells.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>["OC_delta", "OC_average", "Population"]</t>
+          <t>["BC_delta", "Population"]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>{"delta": "OC_delta", "avg": "OC_average", "pop": "Population"}</t>
+          <t>{"delta": "BC_delta", "pop": "Population"}</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>std_delta</t>
+          <t>val</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>pop &gt; 0 &amp;&amp; avg &gt; 0</t>
+          <t>pop &gt; 0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>weighted_mean</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2836,7 +2853,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>delta_oc_per_capita</t>
+          <t>delta_oc</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2846,7 +2863,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cell-level OC_delta/population, averaged across populated cells.</t>
+          <t>Organic carbon delta, population-weighted.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2861,7 +2878,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>delta</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2871,10 +2888,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>weighted_mean</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2883,37 +2904,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hdd_18</t>
+          <t>standard_delta_oc</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Need/heat exposure</t>
+          <t>Heating by combustion</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Heating Degree Days below 18°C, population-weighted.</t>
+          <t>OC delta standardized by average OC, population-weighted.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>["ERA5-Land_HDD", "Population"]</t>
+          <t>["OC_delta", "OC_average", "Population"]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>{"hdd": "ERA5-Land_HDD", "pop": "Population"}</t>
+          <t>{"delta": "OC_delta", "avg": "OC_average", "pop": "Population"}</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>hdd</t>
+          <t>std_delta</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>pop &gt;= 0</t>
+          <t>(pop &gt; 0) &amp;&amp; (avg &gt; 0)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2934,49 +2955,45 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cdd_25</t>
+          <t>delta_oc_per_capita</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Need/heat exposure</t>
+          <t>Heating by combustion</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cooling Degree Days above 25°C, population-weighted.</t>
+          <t>Cell-level OC_delta/population, averaged across populated cells.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>["ERA5-Land_CDD", "Population"]</t>
+          <t>["OC_delta", "Population"]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>{"cdd": "ERA5-Land_CDD", "pop": "Population"}</t>
+          <t>{"delta": "OC_delta", "pop": "Population"}</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>cdd</t>
+          <t>val</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>pop &gt;= 0</t>
+          <t>pop &gt; 0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>weighted_mean</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2985,7 +3002,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>extreme_heat</t>
+          <t>hdd_18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2995,22 +3012,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Average temperature for 6th–10th hottest days, population-weighted.</t>
+          <t>Heating Degree Days below 18°C, population-weighted.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>["ERA5-Land_extreme_heat", "Population"]</t>
+          <t>["ERA5-Land_HDD", "Population"]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>{"heat": "ERA5-Land_extreme_heat", "pop": "Population"}</t>
+          <t>{"hdd": "ERA5-Land_HDD", "pop": "Population"}</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>heat</t>
+          <t>hdd</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3036,7 +3053,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>extreme_cold</t>
+          <t>cdd_25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3046,22 +3063,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Average temperature for 6th–10th coldest days, population-weighted.</t>
+          <t>Cooling Degree Days above 25°C, population-weighted.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>["ERA5-Land_extreme_cold", "Population"]</t>
+          <t>["ERA5-Land_CDD", "Population"]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>{"cold": "ERA5-Land_extreme_cold", "pop": "Population"}</t>
+          <t>{"cdd": "ERA5-Land_CDD", "pop": "Population"}</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>cold</t>
+          <t>cdd</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3083,6 +3100,108 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>extreme_heat</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Need/heat exposure</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Average temperature for 6th–10th hottest days, population-weighted.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>["ERA5-Land_extreme_heat", "Population"]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>{"heat": "ERA5-Land_extreme_heat", "pop": "Population"}</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>pop &gt;= 0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>weighted_mean</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>extreme_cold</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Need/heat exposure</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Average temperature for 6th–10th coldest days, population-weighted.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>["ERA5-Land_extreme_cold", "Population"]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>{"cold": "ERA5-Land_extreme_cold", "pop": "Population"}</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>cold</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>pop &gt;= 0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>weighted_mean</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3095,7 +3214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3514,7 +3633,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita</t>
+          <t>ntl</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3531,24 +3650,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita</t>
+          <t>ntl</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>ntl_res</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>(ntl * res_share * pop) / res_volume</t>
+          <t>ntl * res_share</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ntl_per_res_vol_distrib</t>
+          <t>ntl_per_capita</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3565,24 +3684,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ntl_per_res_vol_distrib</t>
+          <t>ntl_per_capita</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>ntl_res</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(ntl * res_share) / res_volume</t>
+          <t>ntl * res_share</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita_distrib</t>
+          <t>energy_per_vol_per_capita</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3599,12 +3718,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita_distrib</t>
+          <t>energy_per_vol_per_capita</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>proxy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3616,24 +3735,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>standard_delta_pm_25</t>
+          <t>ntl_per_res_vol_distrib</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>std_delta</t>
+          <t>res_share</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>delta / avg</t>
+          <t>res_area / (res_area + nres_area)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>delta_pm_25_per_capita</t>
+          <t>ntl_per_res_vol_distrib</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3643,31 +3762,31 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>delta / pop</t>
+          <t>(ntl * res_share) / res_volume</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>standard_delta_bc</t>
+          <t>energy_per_vol_per_capita_distrib</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>std_delta</t>
+          <t>res_share</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>delta / avg</t>
+          <t>res_area / (res_area + nres_area)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>delta_bc_per_capita</t>
+          <t>energy_per_vol_per_capita_distrib</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3677,14 +3796,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>delta / pop</t>
+          <t>(ntl * res_share * pop) / res_volume</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>standard_delta_oc</t>
+          <t>standard_delta_pm_25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3701,15 +3820,83 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>delta_pm_25_per_capita</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>delta / pop</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>standard_delta_bc</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>std_delta</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>delta / avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>delta_bc_per_capita</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>delta / pop</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>standard_delta_oc</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>std_delta</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>delta / avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>delta_oc_per_capita</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>val</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>delta / pop</t>
         </is>
@@ -3828,7 +4015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4286,83 +4473,83 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita</t>
+          <t>ntl</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ratio_of_sums</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ntl * (res_area / (res_area + nres_area)) * pop</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>res_volume</t>
-        </is>
-      </c>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ntl_per_res_vol_distrib</t>
+          <t>ntl_per_capita</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>weighted_distribution</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>res_volume</t>
-        </is>
-      </c>
+          <t>ratio_of_sums</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ntl * (res_area / (res_area + nres_area))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita_distrib</t>
+          <t>energy_per_vol_per_capita</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>weighted_distribution</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
+          <t>ratio_of_sums</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ntl * (res_area / (res_area + nres_area)) * pop</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>res_volume</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>delta_pm_25</t>
+          <t>ntl_per_res_vol_distrib</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>weighted_mean</t>
+          <t>weighted_distribution</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>res_volume</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4370,12 +4557,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>standard_delta_pm_25</t>
+          <t>energy_per_vol_per_capita_distrib</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>weighted_mean</t>
+          <t>weighted_distribution</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -4390,23 +4577,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>delta_pm_25_per_capita</t>
+          <t>delta_pm_25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>weighted_mean</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>delta_bc</t>
+          <t>standard_delta_pm_25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4426,43 +4617,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>standard_delta_bc</t>
+          <t>delta_pm_25_per_capita</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>weighted_mean</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>delta_bc_per_capita</t>
+          <t>delta_bc</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>weighted_mean</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>delta_oc</t>
+          <t>standard_delta_bc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4482,43 +4673,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>standard_delta_oc</t>
+          <t>delta_bc_per_capita</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>weighted_mean</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>delta_oc_per_capita</t>
+          <t>delta_oc</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>weighted_mean</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hdd_18</t>
+          <t>standard_delta_oc</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4538,27 +4729,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cdd_25</t>
+          <t>delta_oc_per_capita</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>weighted_mean</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>extreme_heat</t>
+          <t>hdd_18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4578,7 +4765,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>extreme_cold</t>
+          <t>cdd_25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4594,6 +4781,46 @@
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>extreme_heat</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>weighted_mean</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>extreme_cold</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>weighted_mean</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4984,7 +5211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5437,51 +5664,51 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita</t>
+          <t>ntl</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita</t>
+          <t>ntl</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ntl*people/m3</t>
+          <t>ntl</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ntl_per_res_vol_distrib</t>
+          <t>ntl_per_capita</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ntl_per_res_vol_p10</t>
+          <t>ntl_per_capita</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ntl/m3</t>
+          <t>ntl/person</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ntl_per_res_vol_distrib</t>
+          <t>energy_per_vol_per_capita</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ntl_per_res_vol_p50</t>
+          <t>energy_per_vol_per_capita</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ntl/m3</t>
+          <t>ntl*people/m3</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5720,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ntl_per_res_vol_p90</t>
+          <t>ntl_per_res_vol_p10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5510,46 +5737,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ntl_per_res_vol_gini</t>
+          <t>ntl_per_res_vol_p50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>ntl/m3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita_distrib</t>
+          <t>ntl_per_res_vol_distrib</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita_p10</t>
+          <t>ntl_per_res_vol_p90</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ntl*people/m3</t>
+          <t>ntl/m3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita_distrib</t>
+          <t>ntl_per_res_vol_distrib</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita_p50</t>
+          <t>ntl_per_res_vol_gini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ntl*people/m3</t>
+          <t>index</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5788,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita_p90</t>
+          <t>energy_per_vol_per_capita_p10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5578,231 +5805,265 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>energy_per_vol_per_capita_gini</t>
+          <t>energy_per_vol_per_capita_p50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>ntl*people/m3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>delta_pm_25</t>
+          <t>energy_per_vol_per_capita_distrib</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>delta_pm_25</t>
+          <t>energy_per_vol_per_capita_p90</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ug/m3</t>
+          <t>ntl*people/m3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>standard_delta_pm_25</t>
+          <t>energy_per_vol_per_capita_distrib</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>standard_delta_pm_25</t>
+          <t>energy_per_vol_per_capita_gini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>index</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>delta_pm_25_per_capita</t>
+          <t>delta_pm_25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>delta_pm_25_per_capita</t>
+          <t>delta_pm_25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ug/m3/person</t>
+          <t>ug/m3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>delta_bc</t>
+          <t>standard_delta_pm_25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>delta_bc</t>
+          <t>standard_delta_pm_25</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ug/m3</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>standard_delta_bc</t>
+          <t>delta_pm_25_per_capita</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>standard_delta_bc</t>
+          <t>delta_pm_25_per_capita</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>ug/m3/person</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>delta_bc_per_capita</t>
+          <t>delta_bc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>delta_bc_per_capita</t>
+          <t>delta_bc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ug/m3/person</t>
+          <t>ug/m3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>delta_oc</t>
+          <t>standard_delta_bc</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>delta_oc</t>
+          <t>standard_delta_bc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ug/m3</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>standard_delta_oc</t>
+          <t>delta_bc_per_capita</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>standard_delta_oc</t>
+          <t>delta_bc_per_capita</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>ug/m3/person</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>delta_oc_per_capita</t>
+          <t>delta_oc</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>delta_oc_per_capita</t>
+          <t>delta_oc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ug/m3/person</t>
+          <t>ug/m3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hdd_18</t>
+          <t>standard_delta_oc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>hdd_18</t>
+          <t>standard_delta_oc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cdd_25</t>
+          <t>delta_oc_per_capita</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>cdd_25</t>
+          <t>delta_oc_per_capita</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>ug/m3/person</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>extreme_heat</t>
+          <t>hdd_18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>extreme_heat</t>
+          <t>hdd_18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>days</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>cdd_25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>cdd_25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>extreme_heat</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>extreme_heat</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>extreme_cold</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>extreme_cold</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>C</t>
         </is>

--- a/pipeline/1_index_construction/indices_manifest.xlsx
+++ b/pipeline/1_index_construction/indices_manifest.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reduce" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reduce_Stats" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outputs" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Administrative_Indicators" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -480,7 +481,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>- Indices_Summary: one row per index (high-level overview)</t>
+          <t>- Indices_Summary: one row per index (high-level overview, including input/reference grid resolutions when raster folders can be inspected)</t>
         </is>
       </c>
     </row>
@@ -520,14 +521,816 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>- Administrative_Indicators: administrative indicators split into basic prediction variables and complex/detailed residual-analysis variables</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tip: You can filter Indices_Summary by group to quickly review definitions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="51" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>indicator</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>used_for_prediction</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>reserved_for_residual_analysis</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>available_in_admin_csv</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>admin_csv</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>admin_split_json</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>admin_csv_rows</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>average_household_age</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>building_state_of_conservation_index</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>homeownership_rate</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>households_by_heating_installation_type_share_of_central</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>listed in split file but not present in admin CSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>households_by_heating_installation_type_share_of_non_central_fireplace</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>listed in split file but not present in admin CSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>households_by_heating_installation_type_share_of_non_central_fixed_appliances</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>listed in split file but not present in admin CSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>households_by_heating_installation_type_share_of_non_central_portable_appliances</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>listed in split file but not present in admin CSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>households_by_heating_installation_type_share_of_none</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>listed in split file but not present in admin CSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>main_heating_energy_source_share_of_electricity</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>main_heating_energy_source_share_of_gas</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>main_heating_energy_source_share_of_other</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>main_heating_energy_source_share_of_petroleum_diesel_and_other_liquid_fuels</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tip: You can filter Indices_Summary by group to quickly review definitions.</t>
-        </is>
-      </c>
+          <t>main_heating_energy_source_share_of_wood_coal_and_other_solid_fuels</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>percentage_overcrowded_households</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>share_of_households_with_air_conditioning</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>complex_detailed</t>
+        </is>
+      </c>
+      <c r="C16" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>share_of_population_over_64_years_old</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>basic_prediction</t>
+        </is>
+      </c>
+      <c r="C17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>share_of_population_under_4_years_old</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>basic_prediction</t>
+        </is>
+      </c>
+      <c r="C18" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>share_of_superior_edu</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>basic_prediction</t>
+        </is>
+      </c>
+      <c r="C19" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>unemployment_rate</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>basic_prediction</t>
+        </is>
+      </c>
+      <c r="C20" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\all_used_adm_indicators.csv</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>E:\git_projects\energy_poverty_from_space\data\adm_data_split.json</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -831,12 +1634,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="57" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="54" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,6 +1673,81 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>folder_path</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tif_count</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>crs</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>resolution_x</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>resolution_y</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>resolution</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>resolution_unit</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>pixel_area</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>unique_resolutions</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>source_years</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>source_year_range</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>release_or_creation_years</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>sample_tif</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>resolution_notes</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>year_inference_notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -872,6 +1765,77 @@
           <t>Building age classes / bins</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\Age</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1975-2020</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1975-2020</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>GHS_AGE_1975052020_GLOBE_R2025A_54009_100_V1_0.tif</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>AGE filename interpreted as multi-epoch source range</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -889,6 +1853,73 @@
           <t>Height raster(s)</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\Height</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>GHS_BUILT_H_AGBH_E2018_GLOBE_R2023A_54009_100_V1_0_R4_C18.tif</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -906,6 +1937,73 @@
           <t>Population raster(s)</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\Population</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>GHS_POP_E2010_GLOBE_R2023A_54009_100_V1_0_R4_C18.tif</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -923,6 +2021,73 @@
           <t>Residential built-up surface</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\Surface</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>GHS_BUILT_S_E2010_GLOBE_R2023A_54009_100_V1_0_R4_C18.tif</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -940,6 +2105,73 @@
           <t>Non-residential built-up surface</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\Surface_NRES</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>GHS_BUILT_S_NRES_E2010_GLOBE_R2023A_54009_100_V1_0_R4_C18.tif</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -957,6 +2189,73 @@
           <t>Residential volume raster(s)</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\Volume</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>GHS_BUILT_V_E2010_GLOBE_R2023A_54009_100_V1_0_R4_C18.tif</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -974,6 +2273,73 @@
           <t>Non-residential volume raster(s)</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\Volume_NRES</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>GHS_BUILT_V_NRES_E2010_GLOBE_R2023A_54009_100_V1_0_R4_C18.tif</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -991,6 +2357,73 @@
           <t>Night-time lights intensity raster(s)</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\NTL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PROJCS["unknown",GEOGCS["unknown",DATUM["WGS_1984",SPHEROID["WGS 84",6378137,298.257223563,AUTHORITY["EPSG","7030"]],AUTHORITY["EPSG","6326"]],PRIMEM["Greenwich",0],UNIT["Degree",0.0174532925199433]],PROJECTION["Mollweide"],PARAMETER["central_meridian",0],PARAMETER["false_easting",0],PARAMETER["false_northing",0],UNIT["metre",1,AUTHORITY["EPSG","9001"]],AXIS["Easting",EAST],AXIS["Northing",NORTH]]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>257.27605219794816</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>257.27605219794816</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>257.276 x 257.276</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>66190.96703456134</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>257.276 x 257.276</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>VNL_v21_npp_201204-201212_global_vcmcfg_c202205302300.median_masked.dat.tif</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1008,6 +2441,69 @@
           <t>PM2.5 annual/overall average raster(s)</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\PM_2_5_average</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1000 x 1000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1000000.0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1000 x 1000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>pm25_average_2010_2012_mollweide.tif</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1025,6 +2521,69 @@
           <t>PM2.5 heating-season delta raster(s)</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\PM_2_5_delta</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1000 x 1000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1000000.0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1000 x 1000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>pm25_delta_JanFeb_minus_rest_2010_2012_mollweide.tif</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1042,6 +2601,69 @@
           <t>Black carbon average raster(s)</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\BC_average</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>100000000.0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>bc_average_2010_2012_mollweide.tif</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1059,6 +2681,69 @@
           <t>Black carbon heating-season delta raster(s)</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\BC_delta</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>100000000.0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>bc_delta_JanFeb_minus_rest_2010_2012_mollweide.tif</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1076,6 +2761,69 @@
           <t>Organic carbon average raster(s)</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\OC_average</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>100000000.0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>oc_average_2010_2012_mollweide.tif</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1093,6 +2841,69 @@
           <t>Organic carbon heating-season delta raster(s)</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\OC_delta</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>100000000.0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>oc_delta_JanFeb_minus_rest_2010_2012_mollweide.tif</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1110,6 +2921,69 @@
           <t>Heating degree days</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\ERA5-Land_HDD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PROJCS["unknown",GEOGCS["unknown",DATUM["WGS_1984",SPHEROID["WGS 84",6378137,298.257223563,AUTHORITY["EPSG","7030"]],AUTHORITY["EPSG","6326"]],PRIMEM["Greenwich",0],UNIT["Degree",0.0174532925199433]],PROJECTION["Mollweide"],PARAMETER["central_meridian",0],PARAMETER["false_easting",0],PARAMETER["false_northing",0],UNIT["metre",1,AUTHORITY["EPSG","9001"]],AXIS["Easting",EAST],AXIS["Northing",NORTH]]</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>8832.357494432195</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>8832.357494432195</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8832.36 x 8832.36</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>78010538.90945257</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>8832.36 x 8832.36</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>PT_hdd_18_ERA5L_skinT_dailyMean_2010_2012_nativegrid.tif</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1127,6 +3001,69 @@
           <t>Cooling degree days</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\ERA5-Land_CDD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PROJCS["unknown",GEOGCS["unknown",DATUM["WGS_1984",SPHEROID["WGS 84",6378137,298.257223563,AUTHORITY["EPSG","7030"]],AUTHORITY["EPSG","6326"]],PRIMEM["Greenwich",0],UNIT["Degree",0.0174532925199433]],PROJECTION["Mollweide"],PARAMETER["central_meridian",0],PARAMETER["false_easting",0],PARAMETER["false_northing",0],UNIT["metre",1,AUTHORITY["EPSG","9001"]],AXIS["Easting",EAST],AXIS["Northing",NORTH]]</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8832.357494432195</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>8832.357494432195</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8832.36 x 8832.36</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>78010538.90945257</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>8832.36 x 8832.36</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>PT_cdd_25_ERA5L_skinT_dailyMean_2010_2012_nativegrid.tif</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1144,6 +3081,69 @@
           <t>6th–10th hottest days mean temperature</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\ERA5-Land_extreme_heat</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PROJCS["unknown",GEOGCS["unknown",DATUM["WGS_1984",SPHEROID["WGS 84",6378137,298.257223563,AUTHORITY["EPSG","7030"]],AUTHORITY["EPSG","6326"]],PRIMEM["Greenwich",0],UNIT["Degree",0.0174532925199433]],PROJECTION["Mollweide"],PARAMETER["central_meridian",0],PARAMETER["false_easting",0],PARAMETER["false_northing",0],UNIT["metre",1,AUTHORITY["EPSG","9001"]],AXIS["Easting",EAST],AXIS["Northing",NORTH]]</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8832.357494432195</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>8832.357494432195</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8832.36 x 8832.36</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>78010538.90945257</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>8832.36 x 8832.36</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>PT_extreme_heat_ERA5L_skinT_dailyMean_2010_2012_nativegrid.tif</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1161,6 +3161,69 @@
           <t>6th–10th coldest days mean temperature</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\ERA5-Land_extreme_cold</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PROJCS["unknown",GEOGCS["unknown",DATUM["WGS_1984",SPHEROID["WGS 84",6378137,298.257223563,AUTHORITY["EPSG","7030"]],AUTHORITY["EPSG","6326"]],PRIMEM["Greenwich",0],UNIT["Degree",0.0174532925199433]],PROJECTION["Mollweide"],PARAMETER["central_meridian",0],PARAMETER["false_easting",0],PARAMETER["false_northing",0],UNIT["metre",1,AUTHORITY["EPSG","9001"]],AXIS["Easting",EAST],AXIS["Northing",NORTH]]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>8832.357494432195</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>8832.357494432195</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8832.36 x 8832.36</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>78010538.90945257</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>8832.36 x 8832.36</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>PT_extreme_cold_ERA5L_skinT_dailyMean_2010_2012_nativegrid.tif</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1178,6 +3241,73 @@
           <t>Greenness vegetation proxy (if used later)</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\Greenness</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>EMC_BUILT_GREENNESS_E2022_GLOBE_R2025A_54009_100_V1_0_R4_C18.tif</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1195,6 +3325,73 @@
           <t>Settlement model degree of urbanization (if used later)</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>E:\OneDrive\Studia\Studia magisterskie\Masterarbeit 2 - Sozialwissenschaften\data\Sat_data_curated\SMOD</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ESRI:54009</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1000 x 1000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>CRS units; meters for Mollweide</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1000000.0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1000 x 1000</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>GHS_SMOD_E2010_GLOBE_R2023A_54009_1000_V2_0_R4_C18.tif</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1207,7 +3404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1215,14 +3412,20 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="49" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="49" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1248,45 +3451,75 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>input_grid_resolutions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>reference_grid_folder</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>reference_grid_resolution</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>reference_grid_pixel_area</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>input_source_years</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>input_source_year_range</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>bind</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>cell_value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>cell_mask</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>reduce_method</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>reduce_weight</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>reduce_numerator</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>reduce_denominator</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>reduce_condition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1315,37 +3548,67 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Surface=100 x 100; Surface_NRES=100 x 100</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Surface</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Surface=2010; Surface_NRES=2010</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>{"res_surface": "Surface", "nres_surface": "Surface_NRES"}</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>res_surface / built_surface</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>built_surface &gt; 0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>ratio_of_sums</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>res_surface</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>res_surface + nres_surface</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1370,33 +3633,63 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Height=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Height=2018; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2010-2018</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>{"height": "Height", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>height</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>res_volume &gt; 0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1421,33 +3714,63 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Height=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Height=2018; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2010-2018</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>{"height": "Height", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>inv_h</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>res_volume &gt; 0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1472,37 +3795,67 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Volume=100 x 100; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Volume=2010; Population=2010</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>{"res_volume": "Volume", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>res_volume / pop</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>(res_volume &gt; 0) &amp;&amp; (pop &gt; 0)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>ratio_of_sums</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1527,33 +3880,63 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Volume=100 x 100; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Volume=2010; Population=2010</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>{"res_volume": "Volume", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>res_volume / pop</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>(res_volume &gt; 0) &amp;&amp; (pop &gt; 0)</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>weighted_distribution</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1578,33 +3961,63 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Age=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Age=1975-2020; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1975-2020</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>{"age_class": "Age", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>age_years</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>(res_volume &gt; 0) &amp;&amp; (mid_year != null)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1629,37 +4042,67 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Age=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Age=1975-2020; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1975-2020</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>{"age_class": "Age", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>is_pre</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>res_volume &gt; 0</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>weighted_share</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>is_pre == 1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1684,37 +4127,67 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Age=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Age=1975-2020; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1975-2020</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>{"age_class": "Age", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>is_bin</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>res_volume &gt; 0</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>weighted_share</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>is_bin == 1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1739,37 +4212,67 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Age=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Age=1975-2020; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1975-2020</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>{"age_class": "Age", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>is_bin</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>res_volume &gt; 0</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>weighted_share</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>is_bin == 1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1794,37 +4297,67 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Age=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Age=1975-2020; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1975-2020</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>{"age_class": "Age", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>is_bin</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>res_volume &gt; 0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>weighted_share</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>is_bin == 1</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1849,37 +4382,67 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Age=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Age=1975-2020; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1975-2020</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>{"age_class": "Age", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>is_bin</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>res_volume &gt; 0</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>weighted_share</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>is_bin == 1</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1904,29 +4467,59 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Volume=2010</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>{"res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>vol_density</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>res_volume &gt; 0</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1951,33 +4544,63 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Surface=100 x 100; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Surface</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Surface=2010; Population=2010</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>{"res_area": "Surface", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>built_up_density</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>(res_area &gt; 0) &amp;&amp; (pop &gt; 0)</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2002,37 +4625,67 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Population=100 x 100; Surface=100 x 100</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Population=2010; Surface=2010</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>{"pop": "Population", "res_area": "Surface"}</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>pop / res_area</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>(pop &gt; 0) &amp;&amp; (res_area &gt; 0)</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>ratio_of_sums</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>res_area</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2057,33 +4710,63 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Population=100 x 100; Surface=100 x 100</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Population=2010; Surface=2010</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>{"pop": "Population", "res_area": "Surface"}</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>pop / res_area</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>(pop &gt; 0) &amp;&amp; (res_area &gt; 0)</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>weighted_distribution</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2108,33 +4791,63 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Age=100 x 100; Height=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Age=1975-2020; Height=2018; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1975-2020</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>{"age_class": "Age", "height": "Height", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>interaction</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>(res_volume &gt; 0) &amp;&amp; (mid_year != null)</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2159,33 +4872,63 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Age=100 x 100; Height=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Age=1975-2020; Height=2018; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1975-2020</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>{"age_class": "Age", "height": "Height", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>interaction</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>(res_volume &gt; 0) &amp;&amp; (mid_year != null)</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2210,33 +4953,63 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Age=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>100 x 100</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Age=1975-2020; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1975-2020</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>{"age_class": "Age", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>interaction</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>(res_volume &gt; 0) &amp;&amp; (mid_year != null)</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2261,37 +5034,67 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>NTL=257.276 x 257.276; Surface=100 x 100; Surface_NRES=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NTL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>257.276 x 257.276</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>66190.96703456134</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NTL=2012; Surface=2010; Surface_NRES=2010; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>{"ntl": "NTL", "res_area": "Surface", "nres_area": "Surface_NRES", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>ntl_res / res_volume</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>(res_volume &gt; 0) &amp;&amp; ((res_area + nres_area) &gt; 0)</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>ratio_of_sums</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>ntl * (res_area / (res_area + nres_area))</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2316,29 +5119,59 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>NTL=257.276 x 257.276; Surface=100 x 100; Surface_NRES=100 x 100</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NTL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>257.276 x 257.276</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>66190.96703456134</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NTL=2012; Surface=2010; Surface_NRES=2010</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>{"ntl": "NTL", "res_area": "Surface", "nres_area": "Surface_NRES"}</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>ntl_res</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>((res_area + nres_area) &gt; 0)</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>sum</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2363,37 +5196,67 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>NTL=257.276 x 257.276; Surface=100 x 100; Surface_NRES=100 x 100; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NTL</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>257.276 x 257.276</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>66190.96703456134</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NTL=2012; Surface=2010; Surface_NRES=2010; Population=2010</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>{"ntl": "NTL", "res_area": "Surface", "nres_area": "Surface_NRES", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>ntl_res / pop</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>(pop &gt; 0) &amp;&amp; ((res_area + nres_area) &gt; 0)</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>ratio_of_sums</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
         <is>
           <t>ntl * (res_area / (res_area + nres_area))</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2418,37 +5281,67 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>NTL=257.276 x 257.276; Surface=100 x 100; Surface_NRES=100 x 100; Population=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NTL</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>257.276 x 257.276</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>66190.96703456134</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NTL=2012; Surface=2010; Surface_NRES=2010; Population=2010; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>{"ntl": "NTL", "res_area": "Surface", "nres_area": "Surface_NRES", "pop": "Population", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>proxy</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>(res_volume &gt; 0) &amp;&amp; (pop &gt; 0) &amp;&amp; ((res_area + nres_area) &gt; 0)</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>ratio_of_sums</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
         <is>
           <t>ntl * (res_area / (res_area + nres_area)) * pop</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2473,33 +5366,63 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>NTL=257.276 x 257.276; Surface=100 x 100; Surface_NRES=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NTL</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>257.276 x 257.276</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>66190.96703456134</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NTL=2012; Surface=2010; Surface_NRES=2010; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>{"ntl": "NTL", "res_area": "Surface", "nres_area": "Surface_NRES", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>val</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>(res_volume &gt; 0) &amp;&amp; ((res_area + nres_area) &gt; 0)</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>weighted_distribution</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>res_volume</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2524,33 +5447,63 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>NTL=257.276 x 257.276; Surface=100 x 100; Surface_NRES=100 x 100; Population=100 x 100; Volume=100 x 100</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NTL</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>257.276 x 257.276</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>66190.96703456134</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>NTL=2012; Surface=2010; Surface_NRES=2010; Population=2010; Volume=2010</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>{"ntl": "NTL", "res_area": "Surface", "nres_area": "Surface_NRES", "pop": "Population", "res_volume": "Volume"}</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>val</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>(res_volume &gt; 0) &amp;&amp; (pop &gt; 0) &amp;&amp; ((res_area + nres_area) &gt; 0)</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>weighted_distribution</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2575,33 +5528,63 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>PM_2_5_delta=1000 x 1000; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PM_2_5_delta</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1000 x 1000</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1000000.0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PM_2_5_delta=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>{"delta": "PM_2_5_delta", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>pop &gt; 0</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2626,33 +5609,63 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>PM_2_5_delta=1000 x 1000; PM_2_5_average=1000 x 1000; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PM_2_5_delta</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1000 x 1000</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1000000.0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PM_2_5_delta=2010-2012; PM_2_5_average=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>{"delta": "PM_2_5_delta", "avg": "PM_2_5_average", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>std_delta</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>(pop &gt; 0) &amp;&amp; (avg &gt; 0)</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2677,29 +5690,59 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>PM_2_5_delta=1000 x 1000; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PM_2_5_delta</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1000 x 1000</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1000000.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>PM_2_5_delta=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>{"delta": "PM_2_5_delta", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>val</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>pop &gt; 0</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2724,33 +5767,63 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>BC_delta=10000 x 10000; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BC_delta</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>100000000.0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>BC_delta=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>{"delta": "BC_delta", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>pop &gt; 0</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2775,33 +5848,63 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>BC_delta=10000 x 10000; BC_average=10000 x 10000; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>BC_delta</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>100000000.0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>BC_delta=2010-2012; BC_average=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>{"delta": "BC_delta", "avg": "BC_average", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>std_delta</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>(pop &gt; 0) &amp;&amp; (avg &gt; 0)</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2826,29 +5929,59 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>BC_delta=10000 x 10000; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>BC_delta</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>100000000.0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>BC_delta=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>{"delta": "BC_delta", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>val</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>pop &gt; 0</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2873,33 +6006,63 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>OC_delta=10000 x 10000; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>OC_delta</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>100000000.0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>OC_delta=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>{"delta": "OC_delta", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>pop &gt; 0</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2924,33 +6087,63 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>OC_delta=10000 x 10000; OC_average=10000 x 10000; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>OC_delta</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>100000000.0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>OC_delta=2010-2012; OC_average=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>{"delta": "OC_delta", "avg": "OC_average", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>std_delta</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>(pop &gt; 0) &amp;&amp; (avg &gt; 0)</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2975,29 +6168,59 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>OC_delta=10000 x 10000; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>OC_delta</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>10000 x 10000</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>100000000.0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>OC_delta=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>{"delta": "OC_delta", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>val</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>pop &gt; 0</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3022,33 +6245,63 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>ERA5-Land_HDD=8832.36 x 8832.36; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ERA5-Land_HDD</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>8832.36 x 8832.36</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>78010538.90945257</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ERA5-Land_HDD=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>{"hdd": "ERA5-Land_HDD", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>hdd</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>pop &gt;= 0</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3073,33 +6326,63 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>ERA5-Land_CDD=8832.36 x 8832.36; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ERA5-Land_CDD</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>8832.36 x 8832.36</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>78010538.90945257</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ERA5-Land_CDD=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>{"cdd": "ERA5-Land_CDD", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>cdd</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>pop &gt;= 0</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3124,33 +6407,63 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>ERA5-Land_extreme_heat=8832.36 x 8832.36; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ERA5-Land_extreme_heat</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>8832.36 x 8832.36</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>78010538.90945257</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ERA5-Land_extreme_heat=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>{"heat": "ERA5-Land_extreme_heat", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>heat</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>pop &gt;= 0</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3175,33 +6488,63 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>ERA5-Land_extreme_cold=8832.36 x 8832.36; Population=100 x 100</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ERA5-Land_extreme_cold</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>8832.36 x 8832.36</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>78010538.90945257</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ERA5-Land_extreme_cold=2010-2012; Population=2010</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2010-2012</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>{"cold": "ERA5-Land_extreme_cold", "pop": "Population"}</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>cold</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>pop &gt;= 0</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>weighted_mean</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
